--- a/src/test/resources/BookingData.xlsx
+++ b/src/test/resources/BookingData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2492243_cognizant_com/Documents/Desktop/cinebook-self/Testing_CineBook/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_F25DC773A252ABDACC104862791E56B65ADE58FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E07A2C2-1BA3-4E6F-B606-9605D52DC284}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_F25DC773A252ABDACC104862791E56B65ADE58FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8193C8EC-256B-4256-9E96-75D4730F6BDF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,10 +33,10 @@
     <t>show-id</t>
   </si>
   <si>
-    <t>movie-book-1</t>
+    <t>movie-book-3</t>
   </si>
   <si>
-    <t>show-1</t>
+    <t>show-12</t>
   </si>
 </sst>
 </file>
